--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="70">
   <si>
     <t>Mat</t>
   </si>
@@ -85,190 +85,148 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
     <t>CUATRA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CANTU</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
     <t>RAFAEL</t>
   </si>
   <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
     <t>MARIA VALERIA</t>
   </si>
   <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
     <t>DAVID DANIEL</t>
   </si>
   <si>
     <t>JOSE EDUARDO</t>
   </si>
   <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
     <t>JOSMAR JAHIR</t>
   </si>
   <si>
     <t>OSVALDO</t>
   </si>
   <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ITZEEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>GERSON UZIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
   </si>
 </sst>
 </file>
@@ -669,16 +627,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81.25</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -692,16 +653,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.27</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -715,16 +679,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>89.19</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -738,16 +705,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>65.63</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -761,16 +731,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>84.09</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -784,16 +757,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>47.22</v>
+      </c>
+      <c r="H7">
+        <v>6.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -807,16 +783,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>62.16</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +851,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -895,7 +874,7 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -918,7 +897,7 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -941,7 +920,7 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -964,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -987,7 +966,7 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1010,7 +989,7 @@
         <v>37</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1069,16 +1048,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81.25</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1092,16 +1074,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.27</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1115,16 +1100,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>89.19</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1138,16 +1126,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>65.63</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1161,16 +1152,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>84.09</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1184,16 +1178,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>47.22</v>
+      </c>
+      <c r="H7">
+        <v>6.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1207,16 +1204,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>62.16</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1226,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1258,16 +1258,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1281,16 +1281,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1304,16 +1304,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920008</v>
+        <v>21330051920355</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1327,16 +1327,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920049</v>
+        <v>21330051920016</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1350,16 +1350,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920010</v>
+        <v>20330051920022</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1373,16 +1373,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920355</v>
+        <v>21330051920025</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1396,16 +1396,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920078</v>
+        <v>21330051920026</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1419,22 +1419,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920011</v>
+        <v>21330051920357</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1442,22 +1442,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920013</v>
+        <v>21330051920076</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1465,22 +1465,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920391</v>
+        <v>21330051920077</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1488,22 +1488,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920015</v>
+        <v>21330051920092</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1511,22 +1511,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920016</v>
+        <v>21330051920098</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1534,22 +1534,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920022</v>
+        <v>21330051920100</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1557,22 +1557,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920379</v>
+        <v>21330051920102</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1580,22 +1580,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920021</v>
+        <v>21330051920103</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1603,22 +1603,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920025</v>
+        <v>21330051920104</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1626,162 +1626,24 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920026</v>
+        <v>21330051920071</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920027</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920028</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920004</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920012</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920019</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920022</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="121">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -106,6 +112,15 @@
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
     <t>CABALLERO</t>
   </si>
   <si>
@@ -130,9 +145,60 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RUBALCAVA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>COYOHUA</t>
   </si>
   <si>
@@ -151,12 +217,15 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>LEYVA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LAGUNES</t>
   </si>
   <si>
@@ -175,7 +244,31 @@
     <t>QUIÑONES</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>ANGEL FIDEL</t>
   </si>
   <si>
     <t>KEVIN ISAAC</t>
@@ -199,6 +292,15 @@
     <t>OSVALDO</t>
   </si>
   <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
     <t>LUIS ARMANDO</t>
   </si>
   <si>
@@ -226,7 +328,58 @@
     <t>GABRIELA</t>
   </si>
   <si>
+    <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>ADAHIR</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>MARIANA PAOLA</t>
+  </si>
+  <si>
+    <t>BRIANDA RENEE</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NANCY PAOLA</t>
+  </si>
+  <si>
     <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>PEDRO EVER</t>
+  </si>
+  <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1258,22 +1411,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>21330051920175</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1281,22 +1434,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920049</v>
+        <v>21330051920177</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1304,16 +1457,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920355</v>
+        <v>21330051920005</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1327,16 +1480,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920016</v>
+        <v>20330051920049</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1350,16 +1503,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920022</v>
+        <v>21330051920355</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1373,16 +1526,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920025</v>
+        <v>21330051920016</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1396,16 +1549,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920026</v>
+        <v>20330051920022</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1419,22 +1572,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920357</v>
+        <v>21330051920025</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1442,22 +1595,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920076</v>
+        <v>21330051920026</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1465,22 +1618,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920077</v>
+        <v>21330051920252</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1488,22 +1641,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920092</v>
+        <v>21330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1511,22 +1664,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920098</v>
+        <v>21330051920088</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1534,16 +1687,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920100</v>
+        <v>21330051920357</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1557,16 +1710,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920102</v>
+        <v>21330051920076</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1580,16 +1733,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920103</v>
+        <v>21330051920077</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1603,16 +1756,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920104</v>
+        <v>21330051920092</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1626,16 +1779,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920071</v>
+        <v>21330051920098</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1644,6 +1797,512 @@
         <v>15</v>
       </c>
       <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920103</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920197</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920200</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920201</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920289</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920235</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920164</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920166</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920169</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920262</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920273</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051420149</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920285</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920288</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920071</v>
+      </c>
+      <c r="B36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>21330051920186</v>
+      </c>
+      <c r="B37" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920207</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920297</v>
+      </c>
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920306</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="135">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -118,79 +121,97 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>CABALLERO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>APALE</t>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RUBALCAVA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RUBALCAVA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>SOLIS</t>
@@ -214,48 +235,48 @@
     <t>VARGAS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
     <t>ARCADIO</t>
   </si>
   <si>
@@ -265,6 +286,12 @@
     <t>SANDOVAL</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
     <t>JHOSUA LEVY</t>
   </si>
   <si>
@@ -295,91 +322,106 @@
     <t>MELANI PAOLA</t>
   </si>
   <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>ADAHIR</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
+  </si>
+  <si>
     <t>MARIA TERESA</t>
   </si>
   <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
     <t>ANGELINA</t>
   </si>
   <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>ADAHIR</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
+    <t>MARIANA PAOLA</t>
+  </si>
+  <si>
+    <t>BRIANDA RENEE</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NANCY PAOLA</t>
+  </si>
+  <si>
+    <t>PEDRO EVER</t>
+  </si>
+  <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
   </si>
   <si>
     <t>JOSE RAFAEL</t>
   </si>
   <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>MARIANA PAOLA</t>
-  </si>
-  <si>
-    <t>BRIANDA RENEE</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>PEDRO EVER</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
+    <t>KARINA YOSELIN</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1411,16 +1453,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920175</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1434,16 +1476,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920177</v>
+        <v>21330051920175</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1457,22 +1499,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920005</v>
+        <v>21330051920177</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1480,16 +1522,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920049</v>
+        <v>21330051920005</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1503,16 +1545,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920355</v>
+        <v>20330051920049</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1526,16 +1568,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920016</v>
+        <v>21330051920355</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1549,16 +1591,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920022</v>
+        <v>21330051920016</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1572,16 +1614,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920025</v>
+        <v>20330051920022</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1595,16 +1637,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920026</v>
+        <v>21330051920025</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1618,22 +1660,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920252</v>
+        <v>21330051920026</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1641,16 +1683,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920260</v>
+        <v>21330051920252</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1664,16 +1706,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920088</v>
+        <v>21330051920261</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1693,10 +1735,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1716,10 +1758,10 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1739,10 +1781,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1762,10 +1804,10 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1785,10 +1827,10 @@
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1808,10 +1850,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1831,10 +1873,10 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1854,10 +1896,10 @@
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1877,10 +1919,10 @@
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1894,16 +1936,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920197</v>
+        <v>21330051920190</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1917,16 +1959,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920200</v>
+        <v>19330061430023</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1940,7 +1982,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920201</v>
+        <v>21330051920195</v>
       </c>
       <c r="B25" t="s">
         <v>44</v>
@@ -1949,7 +1991,7 @@
         <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1963,22 +2005,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920289</v>
+        <v>21330051920197</v>
       </c>
       <c r="B26" t="s">
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1986,22 +2028,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920235</v>
+        <v>21330051920200</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -2009,91 +2051,91 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920164</v>
+        <v>21330051920201</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920166</v>
+        <v>21330051920289</v>
       </c>
       <c r="B29" t="s">
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920169</v>
+        <v>21330051920299</v>
       </c>
       <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="s">
         <v>33</v>
       </c>
-      <c r="C30" t="s">
-        <v>67</v>
-      </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920262</v>
+        <v>21330051920164</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2101,22 +2143,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920273</v>
+        <v>21330051920166</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2124,22 +2166,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051420149</v>
+        <v>21330051920169</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2147,16 +2189,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920285</v>
+        <v>21330051920260</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2170,16 +2212,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920288</v>
+        <v>21330051920262</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2193,22 +2235,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920071</v>
+        <v>21330051920088</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2216,22 +2258,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920186</v>
+        <v>21330051920273</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2239,22 +2281,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920207</v>
+        <v>21330051420149</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2262,22 +2304,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920297</v>
+        <v>21330051920285</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2285,24 +2327,185 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
+        <v>21330051920288</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920071</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920186</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920207</v>
+      </c>
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>21330051920297</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
         <v>21330051920306</v>
       </c>
-      <c r="B40" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" t="s">
-        <v>120</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="B45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" t="s">
+        <v>132</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
         <v>13</v>
       </c>
-      <c r="G40">
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>20330051920235</v>
+      </c>
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920328</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="130">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>LOYO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -97,43 +100,82 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>CUATRA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CABALLERO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>MADRAZO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
@@ -145,109 +187,82 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>RUBALCAVA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
+    <t>TEMOXTLE</t>
   </si>
   <si>
     <t>CRUZ</t>
@@ -256,9 +271,6 @@
     <t>QUIÑONES</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>TZOPITL</t>
   </si>
   <si>
@@ -268,30 +280,15 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
     <t>OSORIO</t>
   </si>
   <si>
     <t>JUAN GERARDO</t>
   </si>
   <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
     <t>JHOSUA LEVY</t>
   </si>
   <si>
@@ -301,46 +298,85 @@
     <t>KEVIN ISAAC</t>
   </si>
   <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>ADAHIR</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
     <t>RAFAEL</t>
   </si>
   <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>MELANI PAOLA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>ANGELO RENE</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>KARLA GRISELL</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
@@ -352,67 +388,16 @@
     <t>GABRIELA</t>
   </si>
   <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>ADAHIR</t>
-  </si>
-  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>SINAI ANTONIO</t>
+  </si>
+  <si>
     <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>MARIANA PAOLA</t>
-  </si>
-  <si>
-    <t>BRIANDA RENEE</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>PEDRO EVER</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>EDNA</t>
   </si>
   <si>
     <t>ANETTE JOCELYN</t>
@@ -822,10 +807,10 @@
         <v>32</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>6</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -834,7 +819,7 @@
         <v>81.25</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -848,19 +833,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -874,10 +859,10 @@
         <v>37</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>4</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>33</v>
@@ -886,7 +871,7 @@
         <v>89.19</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -900,10 +885,10 @@
         <v>32</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>11</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>21</v>
@@ -912,7 +897,7 @@
         <v>65.63</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -926,10 +911,10 @@
         <v>44</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>7</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
       <c r="F6">
         <v>37</v>
@@ -938,7 +923,7 @@
         <v>84.09</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -952,19 +937,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -978,19 +963,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8">
-        <v>62.16</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1043,16 +1028,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.13</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1066,16 +1054,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
         <v>34</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.27</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1089,16 +1080,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>83.78</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1112,16 +1106,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>71.88</v>
+      </c>
+      <c r="H5">
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1135,16 +1132,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>86.36</v>
+      </c>
+      <c r="H6">
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1158,16 +1158,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1181,16 +1184,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>67.56999999999999</v>
+      </c>
+      <c r="H8">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1243,19 +1249,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>81.25</v>
+        <v>78.13</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1269,10 +1275,10 @@
         <v>44</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>10</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>34</v>
@@ -1281,7 +1287,7 @@
         <v>77.27</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1295,19 +1301,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>89.19</v>
+        <v>83.78</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1321,19 +1327,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>65.63</v>
+        <v>71.88</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1347,19 +1353,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>84.09</v>
+        <v>86.36</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1373,19 +1379,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1399,19 +1405,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8">
-        <v>62.16</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1421,7 +1427,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1459,10 +1465,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1476,16 +1482,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920175</v>
+        <v>21330051920164</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1499,16 +1505,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920177</v>
+        <v>21330051920175</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1522,22 +1528,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>21330051920177</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1545,16 +1551,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920049</v>
+        <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1574,10 +1580,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1591,16 +1597,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920016</v>
+        <v>21330051920018</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1614,16 +1620,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920022</v>
+        <v>21330051920028</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1637,22 +1643,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920025</v>
+        <v>21330051920261</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1660,22 +1666,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920026</v>
+        <v>21330051920072</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1683,22 +1689,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920252</v>
+        <v>21330051920357</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1706,22 +1712,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920261</v>
+        <v>21330051920108</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1729,16 +1735,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920357</v>
+        <v>21330051920082</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1752,16 +1758,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920076</v>
+        <v>21330051920098</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1775,16 +1781,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920077</v>
+        <v>21330051920100</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1798,22 +1804,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920092</v>
+        <v>21330051920240</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1821,22 +1827,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920098</v>
+        <v>21330051920242</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1844,22 +1850,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920100</v>
+        <v>21330051920190</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1867,22 +1873,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920102</v>
+        <v>21330051920197</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1890,22 +1896,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920103</v>
+        <v>21330051920200</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1913,22 +1919,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920104</v>
+        <v>21330051920297</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1936,22 +1942,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920190</v>
+        <v>21330051920308</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1959,183 +1965,180 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330061430023</v>
+        <v>21330051920162</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920195</v>
+        <v>21330051920166</v>
       </c>
       <c r="B25" t="s">
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920197</v>
+        <v>21330051920168</v>
       </c>
       <c r="B26" t="s">
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920200</v>
+        <v>20330051920049</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920201</v>
+        <v>21330051920260</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920289</v>
+        <v>21330051920262</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920299</v>
+        <v>21330051920267</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920164</v>
+        <v>21330051920088</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2143,22 +2146,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920166</v>
+        <v>21330051920285</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2166,22 +2169,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920169</v>
+        <v>20330051920358</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2189,22 +2192,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920260</v>
+        <v>21330051920071</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2212,22 +2215,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920262</v>
+        <v>21330051920102</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2235,22 +2238,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920088</v>
+        <v>21330051920103</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2258,22 +2261,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920273</v>
+        <v>21330051920104</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2281,22 +2284,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051420149</v>
+        <v>19330061430023</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2304,22 +2307,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920285</v>
+        <v>21330051920201</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2327,22 +2330,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920288</v>
+        <v>21330051920207</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2350,22 +2353,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>21330051920071</v>
+        <v>21330051920289</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2373,22 +2376,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>21330051920186</v>
+        <v>21330051920306</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2396,22 +2399,22 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>21330051920207</v>
+        <v>20330051920235</v>
       </c>
       <c r="B43" t="s">
         <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2419,16 +2422,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>21330051920297</v>
+        <v>21330051920328</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2437,75 +2440,6 @@
         <v>13</v>
       </c>
       <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920306</v>
-      </c>
-      <c r="B45" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>20330051920235</v>
-      </c>
-      <c r="B46" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920328</v>
-      </c>
-      <c r="B47" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -85,328 +85,109 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>PALMA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>CABALLERO</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>RANGEL</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
-  </si>
-  <si>
-    <t>ANGEL FIDEL</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
   </si>
   <si>
     <t>LUIS ARMANDO</t>
   </si>
   <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
+    <t>INGRID AMERICA</t>
   </si>
   <si>
     <t>ALDO GEOVANNI</t>
   </si>
   <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
+    <t>ADAHIR</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
   </si>
   <si>
     <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>ADAHIR</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>SALVADOR</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>KARLA GRISELL</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
   </si>
 </sst>
 </file>
@@ -1252,16 +1033,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1278,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>88.64</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1304,16 +1085,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>83.78</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1330,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1356,16 +1137,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>86.36</v>
+        <v>97.73</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1382,16 +1163,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="H7">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1408,13 +1189,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>67.56999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="H8">
         <v>6.5</v>
@@ -1427,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1459,22 +1240,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920156</v>
+        <v>21330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1482,22 +1263,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920164</v>
+        <v>21330051920007</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1505,22 +1286,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920175</v>
+        <v>21330051920026</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1528,22 +1309,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920177</v>
+        <v>21330051920357</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1551,22 +1332,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920005</v>
+        <v>21330051920094</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1574,22 +1355,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920355</v>
+        <v>21330051920098</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1597,22 +1378,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920018</v>
+        <v>21330051920200</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1620,22 +1401,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920028</v>
+        <v>21330051920308</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1643,16 +1424,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920261</v>
+        <v>21330051920282</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
         <v>53</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1661,44 +1442,44 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920072</v>
+        <v>21330051920285</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920357</v>
+        <v>21330051920103</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1707,739 +1488,29 @@
         <v>15</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920108</v>
+        <v>21330051920242</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920082</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920098</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920240</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920242</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920190</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920197</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920200</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920297</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920308</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920162</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" t="s">
-        <v>110</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920166</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920168</v>
-      </c>
-      <c r="B26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920049</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920260</v>
-      </c>
-      <c r="B28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920262</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" t="s">
-        <v>115</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920267</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920088</v>
-      </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" t="s">
-        <v>117</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920285</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920358</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920071</v>
-      </c>
-      <c r="B34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920102</v>
-      </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920103</v>
-      </c>
-      <c r="B36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" t="s">
-        <v>121</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920104</v>
-      </c>
-      <c r="B37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" t="s">
-        <v>83</v>
-      </c>
-      <c r="D37" t="s">
-        <v>122</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>19330061430023</v>
-      </c>
-      <c r="B38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920201</v>
-      </c>
-      <c r="B39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" t="s">
-        <v>124</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920207</v>
-      </c>
-      <c r="B40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920289</v>
-      </c>
-      <c r="B41" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920306</v>
-      </c>
-      <c r="B42" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>20330051920235</v>
-      </c>
-      <c r="B43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" t="s">
-        <v>53</v>
-      </c>
-      <c r="D43" t="s">
-        <v>128</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920328</v>
-      </c>
-      <c r="B44" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="60">
   <si>
     <t>Mat</t>
   </si>
@@ -103,6 +103,12 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>NEPOMUCENO</t>
   </si>
   <si>
@@ -136,9 +142,6 @@
     <t>BRAVO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -170,6 +173,12 @@
   </si>
   <si>
     <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
   </si>
   <si>
     <t>ADAHIR</t>
@@ -1208,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1246,10 +1255,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1269,10 +1278,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1292,10 +1301,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1315,10 +1324,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1338,10 +1347,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1361,10 +1370,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1378,22 +1387,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920200</v>
+        <v>21330051920359</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1401,22 +1410,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920308</v>
+        <v>21330051920237</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1424,68 +1433,68 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920282</v>
+        <v>21330051920200</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920285</v>
+        <v>21330051920308</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920103</v>
+        <v>21330051920282</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1493,7 +1502,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920242</v>
+        <v>21330051920285</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1502,15 +1511,61 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920103</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920242</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
         <v>11</v>
       </c>
-      <c r="G13">
+      <c r="G15">
         <v>1</v>
       </c>
     </row>
